--- a/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,104 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 됐는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 업무를 계속 확인하는 걸 멈출 수가 없어서 왔어요. 저는 회계 일을 하는데, 이미 확인했다는 걸 알면서도 같은 스프레드시트랑 계산을 계속 다시 들여다봐요. 어떤 날은 다들 퇴근한 후에도 몇 시간씩 남아 있어요. 한 번 더 확인 안 하면 뭔가 안 좋은 일이 생길 거고, 그게 다 제 잘못이 될 것 같은 느낌이 들어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 마음속에 불쑥 떠오르는, 불편하게 느껴지거나 자신의 생각 같지 않게 느껴지는 생각이나 이미지가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 대개 업무에 관한 거예요. 숫자가 다 맞다는 걸 알고 나서도, 갑자기 '혹시 숨겨진 실수를 놓친 건 아닐까?' 하는 생각이 들어요. 급여나 세금 관련해서요. 그러면 누군가의 수표가 처리가 안 되거나 회사가 곤란해질 것 같은 생각이 들고요.
+이미 확인했다는 걸 아니까 그 생각을 머릿속에서 밀어내려고 하는데, 바로 다시 돌아와요. 방금 제 눈으로 직접 본 걸 못 믿는 느낌이 들게 만들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 작업을 다시 확인하러 돌아가면, 그게 걱정을 진정시키거나 나쁜 생각이 다시 떠오르는 걸 잠깐이라도 멈추게 하는 데 도움이 되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 잠깐은 도움이 돼요. 스프레드시트를 다시 확인하면 순간적으로는 마음이 좀 편해져요, 뭔가 잡아낸 것 같거나 괜찮다는 게 증명된 것 같아서요. 근데 그러고 나면 다시 의심이 들고, 계산을 한 번 더 봐야 할 것 같은 느낌이 들어요. 그래서 다들 퇴근한 후에도 몇 시간씩 남아 있게 되는 거예요. 멈추면 뭔가 안 좋은 일이 생기고 그게 제 잘못이 될 것 같아서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 실수할지도 모른다는 이런 걱정들이, 그걸 겪고 있는 순간에도 비합리적이거나 과하다고 느껴지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 그러니까, 저도 마음 한편으로는 이게 과하다는 걸 알아요. 숫자가 다 맞는 걸 눈으로 보면서도, 급여나 세금에 숨겨진 실수 하나가 있어서 누군가 수표가 안 나오거나 회사가 곤란해질 거라는 생각이 또 들어요. 밀어내려고 해도 다시 돌아오고, 그러면 방금 본 것조차 믿을 수 없다는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 강박장애 (D016)
 인구통계: 성별 여성 / 나이 23 / 직업상태 bookkeeping accounting or auditing clerk / 최종학력 고등학교 졸업
@@ -575,153 +664,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S066
-배경 서술: 켄네트라는 선임 사무원이 퇴사한 후 회계 사무소에서 월말 결산 업무를 확대해서 맡게 되었고, 급여와 거래처, 세무 신고에 영향을 미치는 계정을 믿고 맡겨준 것에 자부심을 느꼈다. 새로운 책임을 맡으면서 초기에 있던 완벽주의적인 재확인 습관은 숨겨진 오류가 회사나 고객에게 해를 끼칠 거라는 침투적이고 원치 않는 생각으로 발전했고, 이어서 실제 위험 수준과 더 이상 맞지 않는 반복적인 스프레드시트 검토와 암산이 뒤따랐다. 언제부터인지 명확하지 않지만 시간이 지나면서 이 악순환은 심각하게 그녀의 기능을 저해하기 시작했다. 그녀는 늦게까지 남아 있느라 성가대 연습과 청소년센터 관련 약속을 놓쳤고, 그러고도 완성된 업무를 제때 넘기지 못했다. 신고 마감을 놓친 일로 정식 업무 회의가 열린 후, 그녀는 회사의 직원 지원 프로그램을 통해 정신과 진료를 받기로 했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 됐는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 업무를 계속 확인하는 걸 멈출 수가 없어서 왔어요. 저는 회계 일을 하는데, 이미 확인했다는 걸 알면서도 같은 스프레드시트랑 계산을 계속 다시 들여다봐요. 어떤 날은 다들 퇴근한 후에도 몇 시간씩 남아 있어요. 한 번 더 확인 안 하면 뭔가 안 좋은 일이 생길 거고, 그게 다 제 잘못이 될 것 같은 느낌이 들어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 마음속에 불쑥 떠오르는, 불편하게 느껴지거나 자신의 생각 같지 않게 느껴지는 생각이나 이미지가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 대개 업무에 관한 거예요. 숫자가 다 맞다는 걸 알고 나서도, 갑자기 '혹시 숨겨진 실수를 놓친 건 아닐까?' 하는 생각이 들어요. 급여나 세금 관련해서요. 그러면 누군가의 수표가 처리가 안 되거나 회사가 곤란해질 것 같은 생각이 들고요.
-이미 확인했다는 걸 아니까 그 생각을 머릿속에서 밀어내려고 하는데, 바로 다시 돌아와요. 방금 제 눈으로 직접 본 걸 못 믿는 느낌이 들게 만들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 작업을 다시 확인하러 돌아가면, 그게 걱정을 진정시키거나 나쁜 생각이 다시 떠오르는 걸 잠깐이라도 멈추게 하는 데 도움이 되나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 잠깐은 도움이 돼요. 스프레드시트를 다시 확인하면 순간적으로는 마음이 좀 편해져요, 뭔가 잡아낸 것 같거나 괜찮다는 게 증명된 것 같아서요. 근데 그러고 나면 다시 의심이 들고, 계산을 한 번 더 봐야 할 것 같은 느낌이 들어요. 그래서 다들 퇴근한 후에도 몇 시간씩 남아 있게 되는 거예요. 멈추면 뭔가 안 좋은 일이 생기고 그게 제 잘못이 될 것 같아서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 실수할지도 모른다는 이런 걱정들이, 그걸 겪고 있는 순간에도 비합리적이거나 과하다고 느껴지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 그러니까, 저도 마음 한편으로는 이게 과하다는 걸 알아요. 숫자가 다 맞는 걸 눈으로 보면서도, 급여나 세금에 숨겨진 실수 하나가 있어서 누군가 수표가 안 나오거나 회사가 곤란해질 거라는 생각이 또 들어요. 밀어내려고 해도 다시 돌아오고, 그러면 방금 본 것조차 믿을 수 없다는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 켄네트라는 선임 사무원이 퇴사한 후 회계 사무소에서 월말 결산 업무를 확대해서 맡게 되었고, 급여와 거래처, 세무 신고에 영향을 미치는 계정을 믿고 맡겨준 것에 자부심을 느꼈다. 새로운 책임을 맡으면서 초기에 있던 완벽주의적인 재확인 습관은 숨겨진 오류가 회사나 고객에게 해를 끼칠 거라는 침투적이고 원치 않는 생각으로 발전했고, 이어서 실제 위험 수준과 더 이상 맞지 않는 반복적인 스프레드시트 검토와 암산이 뒤따랐다. 언제부터인지 명확하지 않지만 시간이 지나면서 이 악순환은 심각하게 그녀의 기능을 저해하기 시작했다. 그녀는 늦게까지 남아 있느라 성가대 연습과 청소년센터 관련 약속을 놓쳤고, 그러고도 완성된 업무를 제때 넘기지 못했다. 신고 마감을 놓친 일로 정식 업무 회의가 열린 후, 그녀는 회사의 직원 지원 프로그램을 통해 정신과 진료를 받기로 했다.
+표집된 증상 목록:
+  - S065 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - S066 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.; 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42.2)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
@@ -650,6 +650,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -684,11 +689,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S002_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
